--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,80 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>09/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>09/11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -838,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I308"/>
+  <dimension ref="A1:I309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10408,6 +10482,29 @@
         <v>0.2455155058386671</v>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>3.712958105838848</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.3960181843858157</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2.763461339531825</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.2897956881014574</v>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -898,6 +898,80 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>09/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>09/14</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -972,6 +972,80 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>09/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>09/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>09/15</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1046,6 +1046,80 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>09/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>09/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>09/16</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1120,6 +1120,80 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>09/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>09/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>09/17</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1194,6 +1194,80 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>09/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>09/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>09/18</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,80 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>09/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>09/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09/21</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1342,6 +1342,80 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>09/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>09/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>09/22</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1416,6 +1416,80 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>09/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>09/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>09/25</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1490,6 +1490,80 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>09/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>09/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>09/28</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1564,6 +1564,80 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>09/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>09/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>09/29</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1638,6 +1638,47 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>09/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>09/30</t>
         </is>
       </c>
     </row>
@@ -9172,16 +9213,16 @@
         <v>0.01701554703132935</v>
       </c>
       <c r="F242" t="n">
-        <v>1.585797683988899</v>
+        <v>1.50732127476314</v>
       </c>
       <c r="G242" t="n">
-        <v>0.4238450694897811</v>
+        <v>0.3462662844492481</v>
       </c>
       <c r="H242" t="n">
-        <v>1.697493947773832</v>
+        <v>1.589367219420712</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3635642517186621</v>
+        <v>0.2568557830324059</v>
       </c>
     </row>
     <row r="243">
@@ -9203,16 +9244,16 @@
         <v>0.150155147991593</v>
       </c>
       <c r="F243" t="n">
-        <v>1.842731871515602</v>
+        <v>1.786311954328568</v>
       </c>
       <c r="G243" t="n">
-        <v>0.332557679444534</v>
+        <v>0.3544995993023159</v>
       </c>
       <c r="H243" t="n">
-        <v>1.709467009196741</v>
+        <v>1.646436382042005</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2069984286937387</v>
+        <v>0.2514882073694436</v>
       </c>
     </row>
     <row r="244">
@@ -9234,16 +9275,16 @@
         <v>0.2459443190924393</v>
       </c>
       <c r="F244" t="n">
-        <v>2.669006722866385</v>
+        <v>2.635440342952511</v>
       </c>
       <c r="G244" t="n">
-        <v>0.5201877934272403</v>
+        <v>0.5430238348004934</v>
       </c>
       <c r="H244" t="n">
-        <v>2.199136019573356</v>
+        <v>2.134146341463405</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4056299940845554</v>
+        <v>0.4040024428054512</v>
       </c>
     </row>
     <row r="245">
@@ -9265,16 +9306,16 @@
         <v>0.8108038414641028</v>
       </c>
       <c r="F245" t="n">
-        <v>3.640285829850343</v>
+        <v>3.577688322194184</v>
       </c>
       <c r="G245" t="n">
-        <v>0.526836923421814</v>
+        <v>0.4989768172006803</v>
       </c>
       <c r="H245" t="n">
-        <v>3.130603204433657</v>
+        <v>3.068278791481682</v>
       </c>
       <c r="I245" t="n">
-        <v>0.5844781311662439</v>
+        <v>0.5876573246619499</v>
       </c>
     </row>
     <row r="246">
@@ -9296,16 +9337,16 @@
         <v>0.6595775780164903</v>
       </c>
       <c r="F246" t="n">
-        <v>4.07246348925363</v>
+        <v>3.970483538896707</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5175714099871831</v>
+        <v>0.4797634654542415</v>
       </c>
       <c r="H246" t="n">
-        <v>3.541119901917589</v>
+        <v>3.435757935671724</v>
       </c>
       <c r="I246" t="n">
-        <v>0.5029844363041214</v>
+        <v>0.4614253951420233</v>
       </c>
     </row>
     <row r="247">
@@ -9327,16 +9368,16 @@
         <v>0.7935672408473149</v>
       </c>
       <c r="F247" t="n">
-        <v>4.306128320705871</v>
+        <v>4.217895847319464</v>
       </c>
       <c r="G247" t="n">
-        <v>0.5407903859486973</v>
+        <v>0.5542755091654472</v>
       </c>
       <c r="H247" t="n">
-        <v>3.861712810213747</v>
+        <v>3.78424903170278</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4662392806593862</v>
+        <v>0.4935687894137342</v>
       </c>
     </row>
     <row r="248">
@@ -9358,16 +9399,16 @@
         <v>0.359083885885525</v>
       </c>
       <c r="F248" t="n">
-        <v>4.473216164011551</v>
+        <v>4.383331102143861</v>
       </c>
       <c r="G248" t="n">
-        <v>0.4560500183891092</v>
+        <v>0.4545956491331493</v>
       </c>
       <c r="H248" t="n">
-        <v>3.92711817566731</v>
+        <v>3.844211288677979</v>
       </c>
       <c r="I248" t="n">
-        <v>0.418957119048291</v>
+        <v>0.4137409926098012</v>
       </c>
     </row>
     <row r="249">
@@ -9389,16 +9430,16 @@
         <v>0.1252476242427747</v>
       </c>
       <c r="F249" t="n">
-        <v>4.580909697720981</v>
+        <v>4.509392581291127</v>
       </c>
       <c r="G249" t="n">
-        <v>0.3825876839715914</v>
+        <v>0.4003224565324981</v>
       </c>
       <c r="H249" t="n">
-        <v>3.958458044715574</v>
+        <v>3.892895489486237</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3218470905389736</v>
+        <v>0.338622202237282</v>
       </c>
     </row>
     <row r="250">
@@ -9420,16 +9461,16 @@
         <v>0.2512571819768494</v>
       </c>
       <c r="F250" t="n">
-        <v>4.737428253233955</v>
+        <v>4.655567929790494</v>
       </c>
       <c r="G250" t="n">
-        <v>0.3282455276546914</v>
+        <v>0.3184335623500179</v>
       </c>
       <c r="H250" t="n">
-        <v>4.013850678303776</v>
+        <v>3.925623754861962</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2120483689641572</v>
+        <v>0.1902323029083552</v>
       </c>
     </row>
     <row r="251">
@@ -9451,16 +9492,16 @@
         <v>0.704331099972122</v>
       </c>
       <c r="F251" t="n">
-        <v>5.336135652537788</v>
+        <v>5.277172827647858</v>
       </c>
       <c r="G251" t="n">
-        <v>0.6616136830434272</v>
+        <v>0.6839596900352962</v>
       </c>
       <c r="H251" t="n">
-        <v>4.436672448273571</v>
+        <v>4.371273943908927</v>
       </c>
       <c r="I251" t="n">
-        <v>0.498900958583004</v>
+        <v>0.5212327016467677</v>
       </c>
     </row>
     <row r="252">
@@ -9482,16 +9523,16 @@
         <v>0.6170384992260303</v>
       </c>
       <c r="F252" t="n">
-        <v>5.93019057933839</v>
+        <v>5.868437553440131</v>
       </c>
       <c r="G252" t="n">
-        <v>0.666293494158654</v>
+        <v>0.6639566395663987</v>
       </c>
       <c r="H252" t="n">
-        <v>4.8908669097107</v>
+        <v>4.797121348421007</v>
       </c>
       <c r="I252" t="n">
-        <v>0.5281881874614314</v>
+        <v>0.5012758924436422</v>
       </c>
     </row>
     <row r="253">
@@ -9513,16 +9554,16 @@
         <v>0.6259571074712644</v>
       </c>
       <c r="F253" t="n">
-        <v>6.141969176624196</v>
+        <v>6.044522653951301</v>
       </c>
       <c r="G253" t="n">
-        <v>0.6197309417040442</v>
+        <v>0.5859918338044556</v>
       </c>
       <c r="H253" t="n">
-        <v>5.214550124650597</v>
+        <v>5.084233587670917</v>
       </c>
       <c r="I253" t="n">
-        <v>0.5849959375282099</v>
+        <v>0.5502796577242508</v>
       </c>
     </row>
     <row r="254">
@@ -9544,16 +9585,16 @@
         <v>0.5529840802300345</v>
       </c>
       <c r="F254" t="n">
-        <v>6.272433512016362</v>
+        <v>6.23485598453779</v>
       </c>
       <c r="G254" t="n">
-        <v>0.547280976192388</v>
+        <v>0.526372136178721</v>
       </c>
       <c r="H254" t="n">
-        <v>5.35843659732218</v>
+        <v>5.325521814482692</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5008167441526545</v>
+        <v>0.4870596693026696</v>
       </c>
     </row>
     <row r="255">
@@ -9575,16 +9616,16 @@
         <v>0.5286706165847699</v>
       </c>
       <c r="F255" t="n">
-        <v>6.545539906103293</v>
+        <v>6.509709604381775</v>
       </c>
       <c r="G255" t="n">
-        <v>0.5903993617304204</v>
+        <v>0.6141394060952488</v>
       </c>
       <c r="H255" t="n">
-        <v>5.602764293293028</v>
+        <v>5.568656926762805</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4393798671143756</v>
+        <v>0.4829103396469359</v>
       </c>
     </row>
     <row r="256">
@@ -9606,16 +9647,16 @@
         <v>0.2716175292170719</v>
       </c>
       <c r="F256" t="n">
-        <v>6.926410970164576</v>
+        <v>6.920266494734562</v>
       </c>
       <c r="G256" t="n">
-        <v>0.8795198773254853</v>
+        <v>0.9305812825262327</v>
       </c>
       <c r="H256" t="n">
-        <v>5.593221924008485</v>
+        <v>5.560286342581766</v>
       </c>
       <c r="I256" t="n">
-        <v>0.3965572429491138</v>
+        <v>0.3960413662982276</v>
       </c>
     </row>
     <row r="257">
@@ -9637,16 +9678,16 @@
         <v>0.5044005313849409</v>
       </c>
       <c r="F257" t="n">
-        <v>6.684755338326309</v>
+        <v>6.633938616310098</v>
       </c>
       <c r="G257" t="n">
-        <v>0.2996444452209701</v>
+        <v>0.2298448765567063</v>
       </c>
       <c r="H257" t="n">
-        <v>5.345023150300299</v>
+        <v>5.288716474561128</v>
       </c>
       <c r="I257" t="n">
-        <v>0.348052500132856</v>
+        <v>0.3288802999813711</v>
       </c>
     </row>
     <row r="258">
@@ -9668,16 +9709,16 @@
         <v>0.5331928925972562</v>
       </c>
       <c r="F258" t="n">
-        <v>6.794545874740021</v>
+        <v>6.784554312522539</v>
       </c>
       <c r="G258" t="n">
-        <v>0.6210152248893985</v>
+        <v>0.6216866629464191</v>
       </c>
       <c r="H258" t="n">
-        <v>5.184136763522318</v>
+        <v>5.169044995323602</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3494929704254801</v>
+        <v>0.3472406298043795</v>
       </c>
     </row>
     <row r="259">
@@ -9699,16 +9740,16 @@
         <v>0.6803326679517774</v>
       </c>
       <c r="F259" t="n">
-        <v>7.243471864656126</v>
+        <v>7.2183163396768</v>
       </c>
       <c r="G259" t="n">
-        <v>0.9634278294741394</v>
+        <v>0.9627299590124982</v>
       </c>
       <c r="H259" t="n">
-        <v>5.31569109508947</v>
+        <v>5.299386299552156</v>
       </c>
       <c r="I259" t="n">
-        <v>0.59189291399524</v>
+        <v>0.6181155400586391</v>
       </c>
     </row>
     <row r="260">
@@ -9730,16 +9771,16 @@
         <v>0.3530011902737717</v>
       </c>
       <c r="F260" t="n">
-        <v>6.750201361938934</v>
+        <v>6.859529873032733</v>
       </c>
       <c r="G260" t="n">
-        <v>-0.006001474648065219</v>
+        <v>0.1184427355122253</v>
       </c>
       <c r="H260" t="n">
-        <v>5.107374057840786</v>
+        <v>5.218819685971487</v>
       </c>
       <c r="I260" t="n">
-        <v>0.220325942505406</v>
+        <v>0.3369124815135738</v>
       </c>
     </row>
     <row r="261">
@@ -9761,16 +9802,16 @@
         <v>0.4903621970395289</v>
       </c>
       <c r="F261" t="n">
-        <v>6.63967758994839</v>
+        <v>6.683455141014072</v>
       </c>
       <c r="G261" t="n">
-        <v>0.2786566178803351</v>
+        <v>0.2348906986712418</v>
       </c>
       <c r="H261" t="n">
-        <v>5.362447330658338</v>
+        <v>5.403329065300899</v>
       </c>
       <c r="I261" t="n">
-        <v>0.5653069058170646</v>
+        <v>0.5145737759249203</v>
       </c>
     </row>
     <row r="262">
@@ -9792,16 +9833,16 @@
         <v>0.5702530898544778</v>
       </c>
       <c r="F262" t="n">
-        <v>6.667939000672507</v>
+        <v>6.693164041183119</v>
       </c>
       <c r="G262" t="n">
-        <v>0.3548342966585682</v>
+        <v>0.3275632034484</v>
       </c>
       <c r="H262" t="n">
-        <v>5.606479327988612</v>
+        <v>5.640449848468254</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4441514278774372</v>
+        <v>0.4156254338470111</v>
       </c>
     </row>
     <row r="263">
@@ -9823,16 +9864,16 @@
         <v>0.3933258669599482</v>
       </c>
       <c r="F263" t="n">
-        <v>6.461602354598139</v>
+        <v>6.505871725383927</v>
       </c>
       <c r="G263" t="n">
-        <v>0.4668955704560718</v>
+        <v>0.5072161081606463</v>
       </c>
       <c r="H263" t="n">
-        <v>5.459759683450094</v>
+        <v>5.509494274375903</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3592772998929128</v>
+        <v>0.3966230870928955</v>
       </c>
     </row>
     <row r="264">
@@ -9854,16 +9895,16 @@
         <v>0.3092862701612242</v>
       </c>
       <c r="F264" t="n">
-        <v>6.030493273542614</v>
+        <v>6.089648674114967</v>
       </c>
       <c r="G264" t="n">
-        <v>0.258652125611647</v>
+        <v>0.2705636884870577</v>
       </c>
       <c r="H264" t="n">
-        <v>5.20808883271644</v>
+        <v>5.285034019752222</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2882861175174778</v>
+        <v>0.2874700910608707</v>
       </c>
     </row>
     <row r="265">
@@ -9885,16 +9926,16 @@
         <v>0.3559477232997654</v>
       </c>
       <c r="F265" t="n">
-        <v>5.520050627946982</v>
+        <v>5.60630932838484</v>
       </c>
       <c r="G265" t="n">
-        <v>0.1353363107321703</v>
+        <v>0.1277268843944857</v>
       </c>
       <c r="H265" t="n">
-        <v>4.966881473370544</v>
+        <v>5.070992092020132</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3543878015085156</v>
+        <v>0.3458633710951009</v>
       </c>
     </row>
     <row r="266">
@@ -9916,16 +9957,16 @@
         <v>0.4140759271916483</v>
       </c>
       <c r="F266" t="n">
-        <v>5.507734586232882</v>
+        <v>5.555654164965662</v>
       </c>
       <c r="G266" t="n">
-        <v>0.5355453439654045</v>
+        <v>0.4781536174095269</v>
       </c>
       <c r="H266" t="n">
-        <v>4.937665213974429</v>
+        <v>5.001699128972836</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4728435597510128</v>
+        <v>0.420789750519579</v>
       </c>
     </row>
     <row r="267">
@@ -9947,16 +9988,16 @@
         <v>0.4893570621394172</v>
       </c>
       <c r="F267" t="n">
-        <v>5.197803844154003</v>
+        <v>5.19978830378407</v>
       </c>
       <c r="G267" t="n">
-        <v>0.2949133744475585</v>
+        <v>0.2749331584523063</v>
       </c>
       <c r="H267" t="n">
-        <v>4.855603371625716</v>
+        <v>4.861964009184616</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3608357091187564</v>
+        <v>0.349188774858411</v>
       </c>
     </row>
     <row r="268">
@@ -9978,16 +10019,16 @@
         <v>0.3367058722950844</v>
       </c>
       <c r="F268" t="n">
-        <v>4.428273156924578</v>
+        <v>4.491151409220007</v>
       </c>
       <c r="G268" t="n">
-        <v>0.14157779658035</v>
+        <v>0.250702217750387</v>
       </c>
       <c r="H268" t="n">
-        <v>4.783286394955444</v>
+        <v>4.864946324252917</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3273155881929002</v>
+        <v>0.398896668788451</v>
       </c>
     </row>
     <row r="269">
@@ -10009,16 +10050,16 @@
         <v>0.4545350273802429</v>
       </c>
       <c r="F269" t="n">
-        <v>4.476012960317743</v>
+        <v>4.532296316964279</v>
       </c>
       <c r="G269" t="n">
-        <v>0.3454968294600791</v>
+        <v>0.2693118329932132</v>
       </c>
       <c r="H269" t="n">
-        <v>4.789642299240104</v>
+        <v>4.853416741769601</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3541393737057863</v>
+        <v>0.3178494441861579</v>
       </c>
     </row>
     <row r="270">
@@ -10040,16 +10081,16 @@
         <v>0.3647229997324919</v>
       </c>
       <c r="F270" t="n">
-        <v>4.003462454014284</v>
+        <v>4.097018223412285</v>
       </c>
       <c r="G270" t="n">
-        <v>0.1659010762728119</v>
+        <v>0.2026925579300398</v>
       </c>
       <c r="H270" t="n">
-        <v>4.731625374880166</v>
+        <v>4.833980505586832</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2939343406269446</v>
+        <v>0.3286396845058936</v>
       </c>
     </row>
     <row r="271">
@@ -10071,16 +10112,16 @@
         <v>0.2177785289873002</v>
       </c>
       <c r="F271" t="n">
-        <v>3.284521339529123</v>
+        <v>3.345578137874217</v>
       </c>
       <c r="G271" t="n">
-        <v>0.2655014565126734</v>
+        <v>0.2339152078182583</v>
       </c>
       <c r="H271" t="n">
-        <v>4.383786808421353</v>
+        <v>4.442869269206207</v>
       </c>
       <c r="I271" t="n">
-        <v>0.2578033808352087</v>
+        <v>0.2427327168426086</v>
       </c>
     </row>
     <row r="272">
@@ -10102,16 +10143,16 @@
         <v>0.2069265248668462</v>
       </c>
       <c r="F272" t="n">
-        <v>3.40904219289897</v>
+        <v>3.361337333904846</v>
       </c>
       <c r="G272" t="n">
-        <v>0.1145522914608677</v>
+        <v>0.1337098247653934</v>
       </c>
       <c r="H272" t="n">
-        <v>4.299124123250864</v>
+        <v>4.236075982487053</v>
       </c>
       <c r="I272" t="n">
-        <v>0.1390401206131209</v>
+        <v>0.1382488479262811</v>
       </c>
     </row>
     <row r="273">
@@ -10133,16 +10174,16 @@
         <v>0.2006732263076128</v>
       </c>
       <c r="F273" t="n">
-        <v>3.43205991996991</v>
+        <v>3.438130751599333</v>
       </c>
       <c r="G273" t="n">
-        <v>0.3009775551999549</v>
+        <v>0.3093612891988951</v>
       </c>
       <c r="H273" t="n">
-        <v>3.828203615670223</v>
+        <v>3.830001388310422</v>
       </c>
       <c r="I273" t="n">
-        <v>0.111244939609878</v>
+        <v>0.1229971133330565</v>
       </c>
     </row>
     <row r="274">
@@ -10164,16 +10205,16 @@
         <v>0.3097745332385715</v>
       </c>
       <c r="F274" t="n">
-        <v>3.44889282701859</v>
+        <v>3.491692737858787</v>
       </c>
       <c r="G274" t="n">
-        <v>0.3711664048937635</v>
+        <v>0.3795144860431199</v>
       </c>
       <c r="H274" t="n">
-        <v>3.687774208035388</v>
+        <v>3.738107788156597</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3082990082631021</v>
+        <v>0.3267536895589229</v>
       </c>
     </row>
     <row r="275">
@@ -10195,16 +10236,16 @@
         <v>0.2956150435211136</v>
       </c>
       <c r="F275" t="n">
-        <v>3.02326173050993</v>
+        <v>3.100032230157246</v>
       </c>
       <c r="G275" t="n">
-        <v>0.05353363147448942</v>
+        <v>0.1268502425805007</v>
       </c>
       <c r="H275" t="n">
-        <v>3.474062854979176</v>
+        <v>3.558948582445387</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1524263272751458</v>
+        <v>0.2232347379907296</v>
       </c>
     </row>
     <row r="276">
@@ -10226,16 +10267,16 @@
         <v>0.3002019540418122</v>
       </c>
       <c r="F276" t="n">
-        <v>2.765089998646619</v>
+        <v>2.888657683491092</v>
       </c>
       <c r="G276" t="n">
-        <v>0.007408382996931806</v>
+        <v>0.06499008695508568</v>
       </c>
       <c r="H276" t="n">
-        <v>3.290743871150426</v>
+        <v>3.437178166838328</v>
       </c>
       <c r="I276" t="n">
-        <v>0.1106111891950201</v>
+        <v>0.1695464632109234</v>
       </c>
     </row>
     <row r="277">
@@ -10257,16 +10298,16 @@
         <v>0.2570488360777556</v>
       </c>
       <c r="F277" t="n">
-        <v>2.767265846736033</v>
+        <v>2.862163349440761</v>
       </c>
       <c r="G277" t="n">
-        <v>0.1374564789740962</v>
+        <v>0.101943503568025</v>
       </c>
       <c r="H277" t="n">
-        <v>3.1123879882345</v>
+        <v>3.225199490262831</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1811022313788824</v>
+        <v>0.1402198713959635</v>
       </c>
     </row>
     <row r="278">
@@ -10288,16 +10329,16 @@
         <v>0.3588818467727739</v>
       </c>
       <c r="F278" t="n">
-        <v>2.698751449360604</v>
+        <v>2.747650036153293</v>
       </c>
       <c r="G278" t="n">
-        <v>0.4685188229492043</v>
+        <v>0.366294349540075</v>
       </c>
       <c r="H278" t="n">
-        <v>3.159014510020852</v>
+        <v>3.224460247838845</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5182765025872449</v>
+        <v>0.4200705917444036</v>
       </c>
     </row>
     <row r="279">
@@ -10319,16 +10360,16 @@
         <v>0.3960944136371047</v>
       </c>
       <c r="F279" t="n">
-        <v>2.705057426970159</v>
+        <v>2.807194063639784</v>
       </c>
       <c r="G279" t="n">
-        <v>0.3010717499795534</v>
+        <v>0.3330442040488935</v>
       </c>
       <c r="H279" t="n">
-        <v>3.059467984974007</v>
+        <v>3.178442605559084</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2639893744276867</v>
+        <v>0.3044529335566537</v>
       </c>
     </row>
     <row r="280">
@@ -10350,16 +10391,16 @@
         <v>0.3891445158509699</v>
       </c>
       <c r="F280" t="n">
-        <v>2.927939232712617</v>
+        <v>2.951557324947318</v>
       </c>
       <c r="G280" t="n">
-        <v>0.3588965562244084</v>
+        <v>0.3914756184091539</v>
       </c>
       <c r="H280" t="n">
-        <v>3.122173857921662</v>
+        <v>3.145526015469802</v>
       </c>
       <c r="I280" t="n">
-        <v>0.3883591005208187</v>
+        <v>0.3668668256971319</v>
       </c>
     </row>
     <row r="281">
@@ -10381,16 +10422,16 @@
         <v>0.2705245081946694</v>
       </c>
       <c r="F281" t="n">
-        <v>2.826154012888593</v>
+        <v>2.838529936773271</v>
       </c>
       <c r="G281" t="n">
-        <v>0.2462653814268689</v>
+        <v>0.1592292006856511</v>
       </c>
       <c r="H281" t="n">
-        <v>3.006720905553606</v>
+        <v>3.017586436450337</v>
       </c>
       <c r="I281" t="n">
-        <v>0.2417854420575516</v>
+        <v>0.1934172567532144</v>
       </c>
     </row>
     <row r="282">
@@ -10412,16 +10453,16 @@
         <v>0.1404065493674</v>
       </c>
       <c r="F282" t="n">
-        <v>2.661672908863921</v>
+        <v>2.6971006168369</v>
       </c>
       <c r="G282" t="n">
-        <v>0.005675322885334566</v>
+        <v>0.06488818953840347</v>
       </c>
       <c r="H282" t="n">
-        <v>2.771176406372033</v>
+        <v>2.809484213974356</v>
       </c>
       <c r="I282" t="n">
-        <v>0.06459314495028678</v>
+        <v>0.1259693092955594</v>
       </c>
     </row>
     <row r="283">
@@ -10443,16 +10484,16 @@
         <v>0.09273959037392476</v>
       </c>
       <c r="F283" t="n">
-        <v>2.548373440470164</v>
+        <v>2.569554023752185</v>
       </c>
       <c r="G283" t="n">
-        <v>0.1548464506923475</v>
+        <v>0.1094278141186233</v>
       </c>
       <c r="H283" t="n">
-        <v>2.753161906357326</v>
+        <v>2.779220779220792</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2402294436318897</v>
+        <v>0.2132248419195015</v>
       </c>
     </row>
     <row r="284">
@@ -10474,16 +10515,16 @@
         <v>0.1727441188479562</v>
       </c>
       <c r="F284" t="n">
-        <v>2.594376777467322</v>
+        <v>2.595980791400909</v>
       </c>
       <c r="G284" t="n">
-        <v>0.1594638130469006</v>
+        <v>0.1595090037569635</v>
       </c>
       <c r="H284" t="n">
-        <v>2.806216333768274</v>
+        <v>2.808852445299759</v>
       </c>
       <c r="I284" t="n">
-        <v>0.190744801389009</v>
+        <v>0.1671191110893755</v>
       </c>
     </row>
     <row r="285">
@@ -10505,16 +10546,16 @@
         <v>0.2539662632470074</v>
       </c>
       <c r="F285" t="n">
-        <v>2.412994957427461</v>
+        <v>2.436664902764929</v>
       </c>
       <c r="G285" t="n">
-        <v>0.1236503523630805</v>
+        <v>0.1535961714133283</v>
       </c>
       <c r="H285" t="n">
-        <v>2.873279917118543</v>
+        <v>2.902341595493985</v>
       </c>
       <c r="I285" t="n">
-        <v>0.1765505121592126</v>
+        <v>0.214043883065318</v>
       </c>
     </row>
     <row r="286">
@@ -10536,16 +10577,16 @@
         <v>0.3071149335418299</v>
       </c>
       <c r="F286" t="n">
-        <v>2.260766436883843</v>
+        <v>2.259416983105855</v>
       </c>
       <c r="G286" t="n">
-        <v>0.2219728950915822</v>
+        <v>0.2058260890621666</v>
       </c>
       <c r="H286" t="n">
-        <v>2.838627996468368</v>
+        <v>2.839579185859575</v>
       </c>
       <c r="I286" t="n">
-        <v>0.2745110779026616</v>
+        <v>0.2655621878426162</v>
       </c>
     </row>
     <row r="287">
@@ -10567,16 +10608,16 @@
         <v>0.3114750009353573</v>
       </c>
       <c r="F287" t="n">
-        <v>2.477692535642562</v>
+        <v>2.406278535995465</v>
       </c>
       <c r="G287" t="n">
-        <v>0.2657775200541224</v>
+        <v>0.2706490744768253</v>
       </c>
       <c r="H287" t="n">
-        <v>2.986502108265898</v>
+        <v>2.904729847657528</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2964378857337246</v>
+        <v>0.2867279000826173</v>
       </c>
     </row>
     <row r="288">
@@ -10598,16 +10639,16 @@
         <v>0.2878180840515832</v>
       </c>
       <c r="F288" t="n">
-        <v>2.5878034125423</v>
+        <v>2.491038837186355</v>
       </c>
       <c r="G288" t="n">
-        <v>0.1148649734123763</v>
+        <v>0.1478125351456416</v>
       </c>
       <c r="H288" t="n">
-        <v>2.980710120125618</v>
+        <v>2.874092511926984</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1049809419213288</v>
+        <v>0.1397234606189901</v>
       </c>
     </row>
     <row r="289">
@@ -10629,16 +10670,16 @@
         <v>0.186575837499281</v>
       </c>
       <c r="F289" t="n">
-        <v>2.728094690120009</v>
+        <v>2.647831800262801</v>
       </c>
       <c r="G289" t="n">
-        <v>0.2743968484478998</v>
+        <v>0.2550815779763571</v>
       </c>
       <c r="H289" t="n">
-        <v>2.988589624519045</v>
+        <v>2.903209770162563</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1887675255320076</v>
+        <v>0.1685633402963127</v>
       </c>
     </row>
     <row r="290">
@@ -10660,16 +10701,16 @@
         <v>0.4265929177532435</v>
       </c>
       <c r="F290" t="n">
-        <v>2.607379530393517</v>
+        <v>2.632440305713302</v>
       </c>
       <c r="G290" t="n">
-        <v>0.350458877091353</v>
+        <v>0.3512449593548128</v>
       </c>
       <c r="H290" t="n">
-        <v>2.780138099441509</v>
+        <v>2.81185798797039</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3148249541047976</v>
+        <v>0.3309232032721932</v>
       </c>
     </row>
     <row r="291">
@@ -10691,16 +10732,16 @@
         <v>0.2547452855180321</v>
       </c>
       <c r="F291" t="n">
-        <v>2.710484673485714</v>
+        <v>2.574767765245123</v>
       </c>
       <c r="G291" t="n">
-        <v>0.4018593970514406</v>
+        <v>0.2766637698029761</v>
       </c>
       <c r="H291" t="n">
-        <v>2.968643293811746</v>
+        <v>2.823064900880157</v>
       </c>
       <c r="I291" t="n">
-        <v>0.4478797948421542</v>
+        <v>0.315386529062911</v>
       </c>
     </row>
     <row r="292">
@@ -10722,16 +10763,16 @@
         <v>0.06913185749619633</v>
       </c>
       <c r="F292" t="n">
-        <v>2.359433670898436</v>
+        <v>2.255205413792827</v>
       </c>
       <c r="G292" t="n">
-        <v>0.01588297424575114</v>
+        <v>0.07871511489225824</v>
       </c>
       <c r="H292" t="n">
-        <v>2.670294814316976</v>
+        <v>2.563598216627327</v>
       </c>
       <c r="I292" t="n">
-        <v>0.09748691517839081</v>
+        <v>0.1135981824290866</v>
       </c>
     </row>
     <row r="293">
@@ -10753,16 +10794,16 @@
         <v>0.2385704197242822</v>
       </c>
       <c r="F293" t="n">
-        <v>2.277425997843396</v>
+        <v>2.331108209167065</v>
       </c>
       <c r="G293" t="n">
-        <v>0.1659507229575752</v>
+        <v>0.2335761784077128</v>
       </c>
       <c r="H293" t="n">
-        <v>2.614795918367352</v>
+        <v>2.676438831266559</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1875992879210031</v>
+        <v>0.30365019497538</v>
       </c>
     </row>
     <row r="294">
@@ -10784,16 +10825,16 @@
         <v>0.1304879206780463</v>
       </c>
       <c r="F294" t="n">
-        <v>2.458086065440868</v>
+        <v>2.46334168227027</v>
       </c>
       <c r="G294" t="n">
-        <v>0.1823226317875459</v>
+        <v>0.1941932262232271</v>
       </c>
       <c r="H294" t="n">
-        <v>2.783883382495933</v>
+        <v>2.787445059882687</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2294784146866347</v>
+        <v>0.2342181574838342</v>
       </c>
     </row>
     <row r="295">
@@ -10815,16 +10856,16 @@
         <v>0.2340215299807769</v>
       </c>
       <c r="F295" t="n">
-        <v>2.593512979706802</v>
+        <v>2.612061147817069</v>
       </c>
       <c r="G295" t="n">
-        <v>0.2872289919291005</v>
+        <v>0.2547307132459986</v>
       </c>
       <c r="H295" t="n">
-        <v>2.8073722050588</v>
+        <v>2.825535800174461</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2631369743222756</v>
+        <v>0.2503616334705638</v>
       </c>
     </row>
     <row r="296">
@@ -10846,16 +10887,16 @@
         <v>0.3125209822436803</v>
       </c>
       <c r="F296" t="n">
-        <v>2.605547294239341</v>
+        <v>2.590924891472191</v>
       </c>
       <c r="G296" t="n">
-        <v>0.1712126113473822</v>
+        <v>0.1388779294563269</v>
       </c>
       <c r="H296" t="n">
-        <v>2.86304724556794</v>
+        <v>2.841168044794573</v>
       </c>
       <c r="I296" t="n">
-        <v>0.2450028147572558</v>
+        <v>0.1823472049344854</v>
       </c>
     </row>
     <row r="297">
@@ -10877,16 +10918,16 @@
         <v>0.3097218588179462</v>
       </c>
       <c r="F297" t="n">
-        <v>2.7476208541517</v>
+        <v>2.694303863880343</v>
       </c>
       <c r="G297" t="n">
-        <v>0.2622873345935917</v>
+        <v>0.2545190928718855</v>
       </c>
       <c r="H297" t="n">
-        <v>2.912416347215907</v>
+        <v>2.851342022982895</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2246302301668779</v>
+        <v>0.2239579623782184</v>
       </c>
     </row>
     <row r="298">
@@ -10908,16 +10949,16 @@
         <v>0.2177737336973129</v>
       </c>
       <c r="F298" t="n">
-        <v>2.787442414870656</v>
+        <v>2.783013548563784</v>
       </c>
       <c r="G298" t="n">
-        <v>0.2608155986582039</v>
+        <v>0.2923861698197694</v>
       </c>
       <c r="H298" t="n">
-        <v>2.825069249833967</v>
+        <v>2.817061120020736</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1894029073346237</v>
+        <v>0.2321431391437478</v>
       </c>
     </row>
     <row r="299">
@@ -10931,16 +10972,16 @@
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2.712580525969122</v>
+        <v>2.657412316640162</v>
       </c>
       <c r="G299" t="n">
-        <v>0.1927522037218354</v>
+        <v>0.1481179614579942</v>
       </c>
       <c r="H299" t="n">
-        <v>2.75453840687383</v>
+        <v>2.704820055566337</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2276415079477623</v>
+        <v>0.1772490940601834</v>
       </c>
     </row>
     <row r="300">
@@ -10962,16 +11003,16 @@
         <v>0.1891543438916843</v>
       </c>
       <c r="F300" t="n">
-        <v>2.820189831269992</v>
+        <v>2.710442301830485</v>
       </c>
       <c r="G300" t="n">
-        <v>0.219752719537647</v>
+        <v>0.1995461303701207</v>
       </c>
       <c r="H300" t="n">
-        <v>2.829092786499077</v>
+        <v>2.721209139520431</v>
       </c>
       <c r="I300" t="n">
-        <v>0.1776129138734595</v>
+        <v>0.1557032202256892</v>
       </c>
     </row>
     <row r="301">
@@ -10993,16 +11034,16 @@
         <v>0.2329002576704653</v>
       </c>
       <c r="F301" t="n">
-        <v>2.878083518031027</v>
+        <v>2.777155475900939</v>
       </c>
       <c r="G301" t="n">
-        <v>0.3308571071852118</v>
+        <v>0.3201999297122393</v>
       </c>
       <c r="H301" t="n">
-        <v>2.971110180682146</v>
+        <v>2.872026924749194</v>
       </c>
       <c r="I301" t="n">
-        <v>0.3271383630529812</v>
+        <v>0.3156332686887087</v>
       </c>
     </row>
     <row r="302">
@@ -11024,16 +11065,16 @@
         <v>0.2950448142634121</v>
       </c>
       <c r="F302" t="n">
-        <v>2.875208305094201</v>
+        <v>2.728367205376991</v>
       </c>
       <c r="G302" t="n">
-        <v>0.3476543056246895</v>
+        <v>0.3036082674866547</v>
       </c>
       <c r="H302" t="n">
-        <v>3.104657789335974</v>
+        <v>2.93799003282269</v>
       </c>
       <c r="I302" t="n">
-        <v>0.444927513566773</v>
+        <v>0.3952569169960451</v>
       </c>
     </row>
     <row r="303">
@@ -11055,16 +11096,16 @@
         <v>0.2160502174024082</v>
       </c>
       <c r="F303" t="n">
-        <v>2.873230041057484</v>
+        <v>2.801144947125711</v>
       </c>
       <c r="G303" t="n">
-        <v>0.3999286948838554</v>
+        <v>0.3477046063099065</v>
       </c>
       <c r="H303" t="n">
-        <v>3.049262855088108</v>
+        <v>2.959152653557551</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3939122649955218</v>
+        <v>0.3360099789506465</v>
       </c>
     </row>
     <row r="304">
@@ -11086,16 +11127,16 @@
         <v>0.1957950538511444</v>
       </c>
       <c r="F304" t="n">
-        <v>3.542928831754533</v>
+        <v>3.36540371338454</v>
       </c>
       <c r="G304" t="n">
-        <v>0.6669806004369283</v>
+        <v>0.6280309065455958</v>
       </c>
       <c r="H304" t="n">
-        <v>3.253849776876594</v>
+        <v>3.105222783353567</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2962135839517099</v>
+        <v>0.2556312693763108</v>
       </c>
     </row>
     <row r="305">
@@ -11117,16 +11158,16 @@
         <v>0.376460730477457</v>
       </c>
       <c r="F305" t="n">
-        <v>3.80182322631788</v>
+        <v>3.573947987920389</v>
       </c>
       <c r="G305" t="n">
-        <v>0.4164014631565349</v>
+        <v>0.4358018523500373</v>
       </c>
       <c r="H305" t="n">
-        <v>3.329827413108966</v>
+        <v>3.083872406870403</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2613206744856766</v>
+        <v>0.2828799503991286</v>
       </c>
     </row>
     <row r="306">
@@ -11148,16 +11189,16 @@
         <v>0.2080954496262777</v>
       </c>
       <c r="F306" t="n">
-        <v>4.111410033233098</v>
+        <v>3.823333966204689</v>
       </c>
       <c r="G306" t="n">
-        <v>0.4811143524811712</v>
+        <v>0.4354414105546933</v>
       </c>
       <c r="H306" t="n">
-        <v>3.463709356864597</v>
+        <v>3.161709771256893</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3593433116647615</v>
+        <v>0.3099037829900508</v>
       </c>
     </row>
     <row r="307">
@@ -11179,16 +11220,16 @@
         <v>-0.01666066684318235</v>
       </c>
       <c r="F307" t="n">
-        <v>3.71697056247684</v>
+        <v>3.45301033693679</v>
       </c>
       <c r="G307" t="n">
-        <v>-0.09272207697451629</v>
+        <v>-0.1028641964020527</v>
       </c>
       <c r="H307" t="n">
-        <v>3.343614465473621</v>
+        <v>3.041234252733216</v>
       </c>
       <c r="I307" t="n">
-        <v>0.1467571284778035</v>
+        <v>0.1332860796942947</v>
       </c>
     </row>
     <row r="308">
@@ -11210,16 +11251,16 @@
         <v>0.2154345141564873</v>
       </c>
       <c r="F308" t="n">
-        <v>3.701165721487087</v>
+        <v>3.361543189447302</v>
       </c>
       <c r="G308" t="n">
-        <v>0.155948088304636</v>
+        <v>0.05034094549449808</v>
       </c>
       <c r="H308" t="n">
-        <v>3.344143004033828</v>
+        <v>2.983468262070388</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2455155058386671</v>
+        <v>0.1261839361694106</v>
       </c>
     </row>
     <row r="309">
@@ -11240,10 +11281,18 @@
       <c r="E309" t="n">
         <v>0.2897956881014574</v>
       </c>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
+      <c r="F309" t="n">
+        <v>3.419031824505425</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0.3102796328484869</v>
+      </c>
+      <c r="H309" t="n">
+        <v>3.007595976185606</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0.2474391583994873</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1679,6 +1679,88 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>09/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>10/01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>10/01</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1761,88 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>10/01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>10/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>10/02</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1841,6 +1841,88 @@
         <v>3.02</v>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>10/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>10/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>10/02</t>
         </is>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1923,6 +1923,88 @@
         <v>3.02</v>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>10/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>10/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>10/02</t>
         </is>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2007,6 +2007,88 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>10/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10/05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>10/05</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2089,6 +2089,88 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>10/05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>10/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>10/06</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2171,88 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>10/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>10/07</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2253,88 @@
       <c r="K46" t="inlineStr">
         <is>
           <t>10/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>10/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>10/08</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2335,6 +2335,88 @@
       <c r="K48" t="inlineStr">
         <is>
           <t>10/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J50" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>10/09</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2415,6 +2415,88 @@
         <v>3.02</v>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>10/09</t>
         </is>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2497,6 +2497,88 @@
         <v>3.02</v>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>10/09</t>
         </is>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2579,6 +2579,88 @@
         <v>3.02</v>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>10/09</t>
         </is>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2663,6 +2663,88 @@
       <c r="K56" t="inlineStr">
         <is>
           <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>10/13</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2748,6 +2748,80 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2759,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I309"/>
+  <dimension ref="A1:I310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12360,6 +12434,29 @@
         <v>0.2474391583994873</v>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>4.023310268457836</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.6485480245771891</v>
+      </c>
+      <c r="D310" t="n">
+        <v>2.789202305125871</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0.3348481932704761</v>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2819,6 +2819,80 @@
       <c r="K60" t="inlineStr">
         <is>
           <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2893,6 +2893,80 @@
       <c r="K62" t="inlineStr">
         <is>
           <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>10/16</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2965,6 +2965,80 @@
         <v>3.05</v>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>10/16</t>
         </is>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3041,6 +3041,80 @@
       <c r="K66" t="inlineStr">
         <is>
           <t>10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>10/19</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3115,6 +3115,80 @@
       <c r="K68" t="inlineStr">
         <is>
           <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>10/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>10/20</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3189,6 +3189,80 @@
       <c r="K70" t="inlineStr">
         <is>
           <t>10/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J71" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>10/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>10/21</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3263,6 +3263,80 @@
       <c r="K72" t="inlineStr">
         <is>
           <t>10/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>10/22</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3337,6 +3337,80 @@
       <c r="K74" t="inlineStr">
         <is>
           <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>10/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J76" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>10/23</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3409,6 +3409,80 @@
         <v>3.05</v>
       </c>
       <c r="K76" t="inlineStr">
+        <is>
+          <t>10/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>10/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J78" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>10/23</t>
         </is>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3485,6 +3485,80 @@
       <c r="K78" t="inlineStr">
         <is>
           <t>10/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J80" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>10/26</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3559,6 +3559,80 @@
       <c r="K80" t="inlineStr">
         <is>
           <t>10/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>10/27</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3633,6 +3633,80 @@
       <c r="K82" t="inlineStr">
         <is>
           <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J83" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>10/28</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3707,6 +3707,47 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -13279,16 +13320,16 @@
         <v>0.2154345141564873</v>
       </c>
       <c r="F308" t="n">
-        <v>3.361543189447302</v>
+        <v>3.373362961562099</v>
       </c>
       <c r="G308" t="n">
-        <v>0.05034094549449808</v>
+        <v>0.06178206947051734</v>
       </c>
       <c r="H308" t="n">
-        <v>2.983468262070388</v>
+        <v>2.995338825447313</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1261839361694106</v>
+        <v>0.1377251498434262</v>
       </c>
     </row>
     <row r="309">
@@ -13310,16 +13351,16 @@
         <v>0.2897956881014574</v>
       </c>
       <c r="F309" t="n">
-        <v>3.419031824505425</v>
+        <v>3.444183322984529</v>
       </c>
       <c r="G309" t="n">
-        <v>0.3102796328484869</v>
+        <v>0.3232027563706552</v>
       </c>
       <c r="H309" t="n">
-        <v>3.007595976185606</v>
+        <v>3.034442461664799</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2474391583994873</v>
+        <v>0.2620094046777544</v>
       </c>
     </row>
     <row r="310">
@@ -13340,10 +13381,18 @@
       <c r="E310" t="n">
         <v>0.3348481932704761</v>
       </c>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr"/>
-      <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr"/>
+      <c r="F310" t="n">
+        <v>3.648874225123633</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0.4908404312709447</v>
+      </c>
+      <c r="H310" t="n">
+        <v>3.12115960296202</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0.3165017740958787</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/inflation_nowcast.xlsx
+++ b/docs/downloads/inflation_nowcast.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3748,6 +3748,47 @@
       <c r="K85" t="inlineStr">
         <is>
           <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>10/30</t>
         </is>
       </c>
     </row>
